--- a/research/traditional_assets/database/data/mexico/mexico_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_real_estate_development.xlsx
@@ -588,46 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0178</v>
-      </c>
-      <c r="E2">
-        <v>-0.00102</v>
+        <v>0.0458</v>
       </c>
       <c r="G2">
-        <v>0.1404290429042904</v>
+        <v>-0.05519203413940256</v>
       </c>
       <c r="H2">
-        <v>0.1404290429042904</v>
+        <v>-0.05519203413940256</v>
       </c>
       <c r="I2">
-        <v>-0.04108910891089109</v>
+        <v>-0.1253200568990043</v>
       </c>
       <c r="J2">
-        <v>-0.03797117064647641</v>
+        <v>-0.1253200568990043</v>
       </c>
       <c r="K2">
-        <v>9.42</v>
+        <v>-3.34</v>
       </c>
       <c r="L2">
-        <v>0.1554455445544554</v>
+        <v>-0.04751066856330014</v>
       </c>
       <c r="M2">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="N2">
-        <v>0.01424465825315507</v>
+        <v>0.005656418210017335</v>
       </c>
       <c r="O2">
-        <v>1.210191082802548</v>
+        <v>-1.856287425149701</v>
       </c>
       <c r="P2">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="Q2">
-        <v>0.01424465825315507</v>
+        <v>0.005656418210017335</v>
       </c>
       <c r="R2">
-        <v>1.210191082802548</v>
+        <v>-1.856287425149701</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>99.90000000000001</v>
+        <v>54.9</v>
       </c>
       <c r="V2">
-        <v>0.1248281894289641</v>
+        <v>0.05008667092418576</v>
       </c>
       <c r="W2">
-        <v>0.0525963149078727</v>
+        <v>-0.01900967558338076</v>
       </c>
       <c r="X2">
-        <v>0.08591535408654394</v>
+        <v>0.07173568670639757</v>
       </c>
       <c r="Y2">
-        <v>-0.03331903917867124</v>
+        <v>-0.09074536228977834</v>
       </c>
       <c r="Z2">
-        <v>0.4136518771331058</v>
+        <v>0.8034285714285716</v>
       </c>
       <c r="AA2">
-        <v>-0.01570684601485646</v>
+        <v>-0.1006857142857143</v>
       </c>
       <c r="AB2">
-        <v>0.08538946499666993</v>
+        <v>0.07171388875023971</v>
       </c>
       <c r="AC2">
-        <v>-0.1010963110115264</v>
+        <v>-0.172399603035954</v>
       </c>
       <c r="AD2">
-        <v>11.7</v>
+        <v>0.931</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.7</v>
+        <v>0.931</v>
       </c>
       <c r="AG2">
-        <v>-88.2</v>
+        <v>-53.969</v>
       </c>
       <c r="AH2">
-        <v>0.01440886699507389</v>
+        <v>0.0008486542312842573</v>
       </c>
       <c r="AI2">
-        <v>0.0624332977588047</v>
+        <v>0.005343480781261658</v>
       </c>
       <c r="AJ2">
-        <v>-0.1238590085662126</v>
+        <v>-0.05178715535762779</v>
       </c>
       <c r="AK2">
-        <v>-1.008</v>
+        <v>-0.4522630330760657</v>
       </c>
       <c r="AL2">
-        <v>1.64</v>
+        <v>0.467</v>
       </c>
       <c r="AM2">
-        <v>0.5399999999999998</v>
+        <v>-3.693</v>
       </c>
       <c r="AN2">
-        <v>-8.666666666666666</v>
+        <v>-0.1147965474722565</v>
       </c>
       <c r="AO2">
-        <v>-1.51829268292683</v>
+        <v>-18.86509635974304</v>
       </c>
       <c r="AP2">
-        <v>65.33333333333333</v>
+        <v>6.654623921085081</v>
       </c>
       <c r="AQ2">
-        <v>-4.611111111111113</v>
+        <v>2.385594367722719</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0178</v>
-      </c>
-      <c r="E3">
-        <v>-0.00102</v>
+        <v>0.0458</v>
       </c>
       <c r="G3">
-        <v>0.1404290429042904</v>
+        <v>-0.05519203413940256</v>
       </c>
       <c r="H3">
-        <v>0.1404290429042904</v>
+        <v>-0.05519203413940256</v>
       </c>
       <c r="I3">
-        <v>-0.04108910891089109</v>
+        <v>-0.1253200568990043</v>
       </c>
       <c r="J3">
-        <v>-0.03797117064647641</v>
+        <v>-0.1253200568990043</v>
       </c>
       <c r="K3">
-        <v>9.42</v>
+        <v>-3.34</v>
       </c>
       <c r="L3">
-        <v>0.1554455445544554</v>
+        <v>-0.04751066856330014</v>
       </c>
       <c r="M3">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="N3">
-        <v>0.01424465825315507</v>
+        <v>0.005656418210017335</v>
       </c>
       <c r="O3">
-        <v>1.210191082802548</v>
+        <v>-1.856287425149701</v>
       </c>
       <c r="P3">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="Q3">
-        <v>0.01424465825315507</v>
+        <v>0.005656418210017335</v>
       </c>
       <c r="R3">
-        <v>1.210191082802548</v>
+        <v>-1.856287425149701</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>99.90000000000001</v>
+        <v>54.9</v>
       </c>
       <c r="V3">
-        <v>0.1248281894289641</v>
+        <v>0.05008667092418576</v>
       </c>
       <c r="W3">
-        <v>0.0525963149078727</v>
+        <v>-0.01900967558338076</v>
       </c>
       <c r="X3">
-        <v>0.08591535408654394</v>
+        <v>0.07173568670639757</v>
       </c>
       <c r="Y3">
-        <v>-0.03331903917867124</v>
+        <v>-0.09074536228977834</v>
       </c>
       <c r="Z3">
-        <v>0.4136518771331058</v>
+        <v>0.8034285714285716</v>
       </c>
       <c r="AA3">
-        <v>-0.01570684601485646</v>
+        <v>-0.1006857142857143</v>
       </c>
       <c r="AB3">
-        <v>0.08538946499666993</v>
+        <v>0.07171388875023971</v>
       </c>
       <c r="AC3">
-        <v>-0.1010963110115264</v>
+        <v>-0.172399603035954</v>
       </c>
       <c r="AD3">
-        <v>11.7</v>
+        <v>0.931</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.7</v>
+        <v>0.931</v>
       </c>
       <c r="AG3">
-        <v>-88.2</v>
+        <v>-53.969</v>
       </c>
       <c r="AH3">
-        <v>0.01440886699507389</v>
+        <v>0.0008486542312842573</v>
       </c>
       <c r="AI3">
-        <v>0.0624332977588047</v>
+        <v>0.005343480781261658</v>
       </c>
       <c r="AJ3">
-        <v>-0.1238590085662126</v>
+        <v>-0.05178715535762779</v>
       </c>
       <c r="AK3">
-        <v>-1.008</v>
+        <v>-0.4522630330760657</v>
       </c>
       <c r="AL3">
-        <v>1.64</v>
+        <v>0.467</v>
       </c>
       <c r="AM3">
-        <v>0.5399999999999998</v>
+        <v>-3.693</v>
       </c>
       <c r="AN3">
-        <v>-8.666666666666666</v>
+        <v>-0.1147965474722565</v>
       </c>
       <c r="AO3">
-        <v>-1.51829268292683</v>
+        <v>-18.86509635974304</v>
       </c>
       <c r="AP3">
-        <v>65.33333333333333</v>
+        <v>6.654623921085081</v>
       </c>
       <c r="AQ3">
-        <v>-4.611111111111113</v>
+        <v>2.385594367722719</v>
       </c>
     </row>
   </sheetData>
